--- a/Result/08-05-25/S&P500stock_08-05-25period252RS90.xlsx
+++ b/Result/08-05-25/S&P500stock_08-05-25period252RS90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="117">
   <si>
     <t>Stock</t>
   </si>
@@ -142,202 +142,226 @@
     <t>EM Rating</t>
   </si>
   <si>
-    <t>TKO</t>
-  </si>
-  <si>
-    <t>GEV</t>
+    <t>DASH</t>
+  </si>
+  <si>
+    <t>CCL</t>
+  </si>
+  <si>
+    <t>WBD</t>
+  </si>
+  <si>
+    <t>GILD</t>
+  </si>
+  <si>
+    <t>GLW</t>
+  </si>
+  <si>
+    <t>APH</t>
+  </si>
+  <si>
+    <t>AVGO</t>
+  </si>
+  <si>
+    <t>GE</t>
   </si>
   <si>
     <t>ETR</t>
   </si>
   <si>
+    <t>SCHW</t>
+  </si>
+  <si>
     <t>PLTR</t>
   </si>
   <si>
+    <t>WELL</t>
+  </si>
+  <si>
+    <t>HWM</t>
+  </si>
+  <si>
     <t>RCL</t>
   </si>
   <si>
-    <t>EXPE</t>
-  </si>
-  <si>
-    <t>CAH</t>
-  </si>
-  <si>
-    <t>NFLX</t>
-  </si>
-  <si>
-    <t>HWM</t>
-  </si>
-  <si>
-    <t>WELL</t>
+    <t>JBL</t>
+  </si>
+  <si>
+    <t>BSX</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>TPR</t>
   </si>
   <si>
     <t>NRG</t>
   </si>
   <si>
-    <t>BSX</t>
-  </si>
-  <si>
-    <t>AXON</t>
-  </si>
-  <si>
     <t>BK</t>
   </si>
   <si>
-    <t>PM</t>
-  </si>
-  <si>
-    <t>FTNT</t>
-  </si>
-  <si>
-    <t>VRSN</t>
-  </si>
-  <si>
-    <t>NI</t>
+    <t>EBAY</t>
+  </si>
+  <si>
+    <t>META</t>
+  </si>
+  <si>
+    <t>RL</t>
   </si>
   <si>
     <t>FFIV</t>
   </si>
   <si>
-    <t>RL</t>
-  </si>
-  <si>
-    <t>WMB</t>
-  </si>
-  <si>
-    <t>CHTR</t>
-  </si>
-  <si>
-    <t>TPL</t>
-  </si>
-  <si>
-    <t>MV</t>
+    <t>PWR</t>
+  </si>
+  <si>
+    <t>CME</t>
+  </si>
+  <si>
+    <t>GL</t>
+  </si>
+  <si>
+    <t>ORCL</t>
+  </si>
+  <si>
+    <t>TRMB</t>
   </si>
   <si>
     <t>M</t>
   </si>
   <si>
-    <t>MP</t>
-  </si>
-  <si>
-    <t>2025-05-09</t>
-  </si>
-  <si>
-    <t>2025-07-22</t>
-  </si>
-  <si>
-    <t>2025-07-30</t>
-  </si>
-  <si>
-    <t>2025-08-04</t>
-  </si>
-  <si>
-    <t>2025-07-23</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>2025-07-17</t>
-  </si>
-  <si>
-    <t>2025-07-28</t>
-  </si>
-  <si>
-    <t>2025-05-12</t>
-  </si>
-  <si>
-    <t>2025-08-05</t>
-  </si>
-  <si>
-    <t>2025-07-10</t>
-  </si>
-  <si>
-    <t>2025-07-24</t>
-  </si>
-  <si>
-    <t>2025-05-22</t>
+    <t>2025-08-07</t>
+  </si>
+  <si>
+    <t>2025-08-08</t>
+  </si>
+  <si>
+    <t>2025-10-28</t>
+  </si>
+  <si>
+    <t>2025-10-22</t>
+  </si>
+  <si>
+    <t>2025-09-03</t>
+  </si>
+  <si>
+    <t>2025-10-30</t>
+  </si>
+  <si>
+    <t>2025-10-14</t>
+  </si>
+  <si>
+    <t>2025-09-24</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>2025-08-14</t>
+  </si>
+  <si>
+    <t>2025-08-06</t>
+  </si>
+  <si>
+    <t>2025-10-10</t>
+  </si>
+  <si>
+    <t>2025-10-23</t>
+  </si>
+  <si>
+    <t>2025-09-09</t>
+  </si>
+  <si>
+    <t>Consumer Cyclical</t>
   </si>
   <si>
     <t>Communication Services</t>
   </si>
   <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
     <t>Industrials</t>
   </si>
   <si>
     <t>Utilities</t>
   </si>
   <si>
-    <t>Technology</t>
-  </si>
-  <si>
-    <t>Consumer Cyclical</t>
-  </si>
-  <si>
-    <t>Healthcare</t>
+    <t>Financial Services</t>
   </si>
   <si>
     <t>Real Estate</t>
   </si>
   <si>
-    <t>Financial Services</t>
-  </si>
-  <si>
-    <t>Consumer Defensive</t>
-  </si>
-  <si>
-    <t>Energy</t>
+    <t>Internet Retail</t>
+  </si>
+  <si>
+    <t>Travel Services</t>
   </si>
   <si>
     <t>Entertainment</t>
   </si>
   <si>
-    <t>Specialty Industrial Machinery</t>
+    <t>Drug Manufacturers - General</t>
+  </si>
+  <si>
+    <t>Electronic Components</t>
+  </si>
+  <si>
+    <t>Semiconductors</t>
+  </si>
+  <si>
+    <t>Aerospace &amp; Defense</t>
   </si>
   <si>
     <t>Utilities - Regulated Electric</t>
   </si>
   <si>
+    <t>Capital Markets</t>
+  </si>
+  <si>
     <t>Software - Infrastructure</t>
   </si>
   <si>
-    <t>Travel Services</t>
-  </si>
-  <si>
-    <t>Medical Distribution</t>
-  </si>
-  <si>
-    <t>Aerospace &amp; Defense</t>
-  </si>
-  <si>
     <t>REIT - Healthcare Facilities</t>
   </si>
   <si>
+    <t>Medical Devices</t>
+  </si>
+  <si>
+    <t>Luxury Goods</t>
+  </si>
+  <si>
     <t>Utilities - Independent Power Producers</t>
   </si>
   <si>
-    <t>Medical Devices</t>
-  </si>
-  <si>
     <t>Banks - Diversified</t>
   </si>
   <si>
-    <t>Tobacco</t>
-  </si>
-  <si>
-    <t>Utilities - Regulated Gas</t>
+    <t>Internet Content &amp; Information</t>
   </si>
   <si>
     <t>Apparel Manufacturing</t>
   </si>
   <si>
-    <t>Oil &amp; Gas Midstream</t>
-  </si>
-  <si>
-    <t>Telecom Services</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas E&amp;P</t>
+    <t>Engineering &amp; Construction</t>
+  </si>
+  <si>
+    <t>Financial Data &amp; Stock Exchanges</t>
+  </si>
+  <si>
+    <t>Insurance - Life</t>
+  </si>
+  <si>
+    <t>Scientific &amp; Technical Instruments</t>
   </si>
   <si>
     <t>United States</t>
@@ -698,7 +722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AP24"/>
+  <dimension ref="A1:AP30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:42">
@@ -834,64 +858,61 @@
         <v>42</v>
       </c>
       <c r="B2">
-        <v>98.01192842942345</v>
+        <v>99.00596421471172</v>
       </c>
       <c r="C2">
-        <v>60.83499005964214</v>
+        <v>96.22266401590457</v>
       </c>
       <c r="D2">
-        <v>415</v>
+        <v>281</v>
       </c>
       <c r="E2">
-        <v>421</v>
+        <v>250</v>
       </c>
       <c r="F2">
-        <v>169.68</v>
+        <v>258.02</v>
       </c>
       <c r="G2">
-        <v>0.6463648835520979</v>
+        <v>1.188618760974898</v>
       </c>
       <c r="H2">
-        <v>0.80927375703989</v>
+        <v>1.256304656434504</v>
       </c>
       <c r="I2">
-        <v>2.26</v>
+        <v>1.81</v>
       </c>
       <c r="J2">
-        <v>-0.5277801014078423</v>
+        <v>-0.04433311816086299</v>
       </c>
       <c r="K2">
-        <v>2.61</v>
+        <v>1.83</v>
       </c>
       <c r="L2">
-        <v>-0.2824639929911533</v>
+        <v>-0.07664303129008103</v>
       </c>
       <c r="M2">
-        <v>166.8079986572266</v>
+        <v>249.5639984130859</v>
       </c>
       <c r="N2">
-        <v>155.3935005187988</v>
+        <v>243.1650009155273</v>
       </c>
       <c r="O2">
-        <v>151.2056005859375</v>
+        <v>230.6828997802734</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2">
-        <v>136.5490501022339</v>
+        <v>193.0719751739502</v>
       </c>
       <c r="R2">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="S2">
-        <v>1.03</v>
-      </c>
-      <c r="T2" t="s">
-        <v>65</v>
+        <v>1.05</v>
       </c>
       <c r="U2">
-        <v>7.777777777777777</v>
+        <v>7.222222222222221</v>
       </c>
       <c r="V2" t="b">
         <v>0</v>
@@ -900,61 +921,61 @@
         <v>1</v>
       </c>
       <c r="X2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2">
-        <v>97.37</v>
+        <v>105.91</v>
       </c>
       <c r="Z2">
-        <v>179.09</v>
+        <v>258.73</v>
       </c>
       <c r="AA2">
-        <v>13.84</v>
+        <v>109.3</v>
       </c>
       <c r="AB2">
-        <v>-42.28</v>
+        <v>-1.92</v>
       </c>
       <c r="AC2">
-        <v>14691.76</v>
+        <v>661.77</v>
       </c>
       <c r="AD2">
-        <v>212.13</v>
+        <v>881.48</v>
       </c>
       <c r="AE2">
-        <v>0.23</v>
+        <v>4.41</v>
       </c>
       <c r="AF2">
-        <v>24.14</v>
+        <v>31.43</v>
       </c>
       <c r="AG2">
-        <v>-60.27</v>
+        <v>-10.26</v>
       </c>
       <c r="AH2">
-        <v>157.94</v>
+        <v>202.63</v>
       </c>
       <c r="AI2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="AJ2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="AK2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AL2" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="AM2">
-        <v>0.02</v>
+        <v>0.79</v>
       </c>
       <c r="AN2">
-        <v>3.24</v>
+        <v>1.78</v>
       </c>
       <c r="AO2">
-        <v>16100</v>
+        <v>125.32</v>
       </c>
       <c r="AP2">
-        <v>90.09712668732641</v>
+        <v>93.71428571428572</v>
       </c>
     </row>
     <row r="3" spans="1:42">
@@ -962,58 +983,58 @@
         <v>43</v>
       </c>
       <c r="B3">
-        <v>99.80119284294234</v>
+        <v>96.81908548707754</v>
       </c>
       <c r="C3">
-        <v>81.31212723658051</v>
+        <v>97.4155069582505</v>
       </c>
       <c r="D3">
-        <v>239</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>218</v>
+        <v>29</v>
       </c>
       <c r="F3">
-        <v>406.81</v>
+        <v>29.72</v>
       </c>
       <c r="G3">
-        <v>1.266980214619023</v>
+        <v>0.6131950488052073</v>
       </c>
       <c r="H3">
-        <v>1.89920808207471</v>
+        <v>1.835524241818016</v>
       </c>
       <c r="I3">
-        <v>3.98</v>
+        <v>1.58</v>
       </c>
       <c r="J3">
-        <v>0.8029388795796801</v>
+        <v>-0.3803580024028594</v>
       </c>
       <c r="K3">
-        <v>4.37</v>
+        <v>2.57</v>
       </c>
       <c r="L3">
-        <v>1.210243896862879</v>
+        <v>1.019863269700016</v>
       </c>
       <c r="M3">
-        <v>397.5500061035156</v>
+        <v>29.67999992370606</v>
       </c>
       <c r="N3">
-        <v>353.4365005493164</v>
+        <v>29.49200000762939</v>
       </c>
       <c r="O3">
-        <v>328.3057995605469</v>
+        <v>26.69000007629394</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3">
-        <v>298.2681999206543</v>
+        <v>23.84885004043579</v>
       </c>
       <c r="R3">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="S3">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="U3">
         <v>0</v>
@@ -1022,64 +1043,64 @@
         <v>0</v>
       </c>
       <c r="W3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>150.01</v>
+        <v>13.78</v>
       </c>
       <c r="Z3">
-        <v>447.5</v>
+        <v>31.01</v>
       </c>
       <c r="AA3">
-        <v>111.03</v>
+        <v>40.3</v>
       </c>
       <c r="AB3">
-        <v>5.32</v>
+        <v>-19.76</v>
       </c>
       <c r="AC3">
-        <v>1135.94</v>
+        <v>40.91</v>
       </c>
       <c r="AD3">
-        <v>293.21</v>
+        <v>474.17</v>
       </c>
       <c r="AE3">
-        <v>22.02</v>
-      </c>
-      <c r="AF3">
-        <v>-28.12</v>
-      </c>
-      <c r="AG3">
-        <v>465.71</v>
-      </c>
-      <c r="AH3">
-        <v>-107.42</v>
+        <v>30.02</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>72</v>
       </c>
       <c r="AI3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AJ3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="AL3" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="AM3">
-        <v>6.96</v>
+        <v>1.91</v>
       </c>
       <c r="AN3">
-        <v>6.9</v>
+        <v>1.72</v>
       </c>
       <c r="AO3">
-        <v>-0.86</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="AP3">
-        <v>71.08632125952667</v>
+        <v>58.18243911506971</v>
       </c>
     </row>
     <row r="4" spans="1:42">
@@ -1087,124 +1108,121 @@
         <v>44</v>
       </c>
       <c r="B4">
-        <v>95.62624254473161</v>
+        <v>91.05367793240556</v>
       </c>
       <c r="C4">
-        <v>74.75149105367794</v>
+        <v>97.01789264413519</v>
       </c>
       <c r="D4">
-        <v>199</v>
+        <v>8</v>
       </c>
       <c r="E4">
-        <v>200</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>84.23999999999999</v>
+        <v>12.8</v>
       </c>
       <c r="G4">
-        <v>0.4960334715222028</v>
+        <v>0.2756546239239595</v>
       </c>
       <c r="H4">
-        <v>0.3400558430228489</v>
+        <v>1.67814493500784</v>
       </c>
       <c r="I4">
-        <v>1.48</v>
+        <v>2.02</v>
       </c>
       <c r="J4">
-        <v>-1.13124568580916</v>
+        <v>0.2624722109296554</v>
       </c>
       <c r="K4">
-        <v>1.86</v>
+        <v>2.43</v>
       </c>
       <c r="L4">
-        <v>-0.91856110514486</v>
+        <v>0.812416131674863</v>
       </c>
       <c r="M4">
-        <v>84.07799987792968</v>
+        <v>13.04400005340576</v>
       </c>
       <c r="N4">
-        <v>83.19349975585938</v>
+        <v>12.66799998283386</v>
       </c>
       <c r="O4">
-        <v>83.55659973144532</v>
+        <v>11.26979999542236</v>
       </c>
       <c r="P4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4">
-        <v>73.7012498664856</v>
+        <v>10.1038999915123</v>
       </c>
       <c r="R4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="S4">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>52.06</v>
+        <v>6.64</v>
       </c>
       <c r="Z4">
-        <v>88.38</v>
+        <v>13.87</v>
       </c>
       <c r="AA4">
-        <v>36.29</v>
-      </c>
-      <c r="AB4">
-        <v>-4.94</v>
+        <v>31.67</v>
       </c>
       <c r="AC4">
-        <v>6.21</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="AD4">
-        <v>365.17</v>
+        <v>53.65</v>
       </c>
       <c r="AE4">
-        <v>8.960000000000001</v>
-      </c>
-      <c r="AF4">
-        <v>-55.15</v>
-      </c>
-      <c r="AG4">
-        <v>1208.7</v>
-      </c>
-      <c r="AH4">
-        <v>-34.29</v>
+        <v>-27.69</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>72</v>
       </c>
       <c r="AI4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AJ4" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AK4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AL4" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="AM4">
-        <v>3.09</v>
+        <v>-4.4</v>
       </c>
       <c r="AN4">
-        <v>7.74</v>
+        <v>-0.13</v>
       </c>
       <c r="AO4">
-        <v>150.49</v>
+        <v>97.05</v>
       </c>
       <c r="AP4">
-        <v>39.18414143441594</v>
+        <v>57.26975028268366</v>
       </c>
     </row>
     <row r="5" spans="1:42">
@@ -1212,58 +1230,58 @@
         <v>45</v>
       </c>
       <c r="B5">
-        <v>100</v>
+        <v>93.04174950298211</v>
       </c>
       <c r="C5">
-        <v>52.08747514910537</v>
+        <v>74.55268389662028</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>137</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="F5">
-        <v>110.48</v>
+        <v>114.51</v>
       </c>
       <c r="G5">
-        <v>3.225172252756676</v>
+        <v>0.4136974877920619</v>
       </c>
       <c r="H5">
-        <v>2.233257259810458</v>
+        <v>0.4037461079473384</v>
       </c>
       <c r="I5">
-        <v>6.26</v>
+        <v>1.95</v>
       </c>
       <c r="J5">
-        <v>2.566915203214303</v>
+        <v>0.1602037678994825</v>
       </c>
       <c r="K5">
-        <v>5.74</v>
+        <v>1.96</v>
       </c>
       <c r="L5">
-        <v>2.372181288396984</v>
+        <v>0.11598645401899</v>
       </c>
       <c r="M5">
-        <v>116.7179992675781</v>
+        <v>113.7940017700195</v>
       </c>
       <c r="N5">
-        <v>104.2795001983643</v>
+        <v>111.995499420166</v>
       </c>
       <c r="O5">
-        <v>92.7661996459961</v>
+        <v>110.5584001159668</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5">
-        <v>65.72360002517701</v>
+        <v>101.953099937439</v>
       </c>
       <c r="R5">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="S5">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="U5">
         <v>0</v>
@@ -1272,64 +1290,64 @@
         <v>0</v>
       </c>
       <c r="W5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>20.5</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="Z5">
-        <v>125.41</v>
+        <v>119.96</v>
       </c>
       <c r="AA5">
-        <v>260.72</v>
+        <v>142.44</v>
       </c>
       <c r="AB5">
-        <v>-518.52</v>
+        <v>-38.13</v>
       </c>
       <c r="AC5">
-        <v>39.87</v>
+        <v>73.51000000000001</v>
       </c>
       <c r="AD5">
-        <v>90.45</v>
+        <v>131.24</v>
       </c>
       <c r="AE5">
-        <v>12.41</v>
+        <v>32.51</v>
       </c>
       <c r="AF5">
-        <v>-33.33</v>
+        <v>-25.87</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AH5">
-        <v>20</v>
+        <v>-22.48</v>
       </c>
       <c r="AI5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AJ5" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="AK5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AL5" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="AM5">
-        <v>0.23</v>
+        <v>4.76</v>
       </c>
       <c r="AN5">
-        <v>0.47</v>
+        <v>7.43</v>
       </c>
       <c r="AO5">
-        <v>104.35</v>
+        <v>56.09</v>
       </c>
       <c r="AP5">
-        <v>39.0408778639541</v>
+        <v>54.16100755339973</v>
       </c>
     </row>
     <row r="6" spans="1:42">
@@ -1337,58 +1355,58 @@
         <v>46</v>
       </c>
       <c r="B6">
-        <v>97.01789264413519</v>
+        <v>95.42743538767395</v>
       </c>
       <c r="C6">
-        <v>28.82703777335984</v>
+        <v>95.42743538767395</v>
       </c>
       <c r="D6">
-        <v>303</v>
+        <v>92</v>
       </c>
       <c r="E6">
-        <v>280</v>
+        <v>140</v>
       </c>
       <c r="F6">
-        <v>228.01</v>
+        <v>63.49</v>
       </c>
       <c r="G6">
-        <v>0.470334830364094</v>
+        <v>0.3990866426965328</v>
       </c>
       <c r="H6">
-        <v>1.603775419654329</v>
+        <v>1.184715645963828</v>
       </c>
       <c r="I6">
-        <v>4.49</v>
+        <v>2.92</v>
       </c>
       <c r="J6">
-        <v>1.197512530919004</v>
+        <v>1.577352192746163</v>
       </c>
       <c r="K6">
-        <v>3.98</v>
+        <v>1.96</v>
       </c>
       <c r="L6">
-        <v>0.8794733985429514</v>
+        <v>0.11598645401899</v>
       </c>
       <c r="M6">
-        <v>226.6139984130859</v>
+        <v>62.6740005493164</v>
       </c>
       <c r="N6">
-        <v>208.2219985961914</v>
+        <v>55.97800006866455</v>
       </c>
       <c r="O6">
-        <v>211.5725994873047</v>
+        <v>52.89059989929199</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6">
-        <v>208.6932499694824</v>
+        <v>48.86904991149903</v>
       </c>
       <c r="R6">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="S6">
-        <v>0.98</v>
+        <v>1.06</v>
       </c>
       <c r="U6">
         <v>0</v>
@@ -1400,61 +1418,61 @@
         <v>1</v>
       </c>
       <c r="X6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>130.08</v>
+        <v>37.18</v>
       </c>
       <c r="Z6">
-        <v>277.08</v>
+        <v>63.91</v>
       </c>
       <c r="AA6">
-        <v>61.92</v>
+        <v>54.39</v>
       </c>
       <c r="AB6">
-        <v>4.1</v>
+        <v>-11.42</v>
       </c>
       <c r="AC6">
-        <v>29.09</v>
+        <v>25.53</v>
       </c>
       <c r="AD6">
-        <v>106.46</v>
+        <v>350.33</v>
       </c>
       <c r="AE6">
-        <v>49.55</v>
-      </c>
-      <c r="AF6">
-        <v>31.55</v>
-      </c>
-      <c r="AG6">
-        <v>-51.18</v>
-      </c>
-      <c r="AH6">
-        <v>27.11</v>
+        <v>7.55</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>72</v>
       </c>
       <c r="AI6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AJ6" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AK6" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="AL6" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="AM6">
-        <v>12.29</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AN6">
-        <v>14.29</v>
+        <v>2.31</v>
       </c>
       <c r="AO6">
-        <v>16.27</v>
+        <v>145.74</v>
       </c>
       <c r="AP6">
-        <v>38.36093417011433</v>
+        <v>51.40426851256596</v>
       </c>
     </row>
     <row r="7" spans="1:42">
@@ -1462,58 +1480,58 @@
         <v>47</v>
       </c>
       <c r="B7">
-        <v>92.04771371769384</v>
+        <v>96.22266401590457</v>
       </c>
       <c r="C7">
-        <v>14.51292246520875</v>
+        <v>93.24055666003976</v>
       </c>
       <c r="D7">
-        <v>283</v>
+        <v>77</v>
       </c>
       <c r="E7">
-        <v>298</v>
+        <v>75</v>
       </c>
       <c r="F7">
-        <v>166.56</v>
+        <v>108.63</v>
       </c>
       <c r="G7">
-        <v>0.3248164543923633</v>
+        <v>0.5373804317194795</v>
       </c>
       <c r="H7">
-        <v>1.418398666690766</v>
+        <v>1.372012314413393</v>
       </c>
       <c r="I7">
-        <v>4.75</v>
+        <v>1.63</v>
       </c>
       <c r="J7">
-        <v>1.398667725719443</v>
+        <v>-0.3073091145241648</v>
       </c>
       <c r="K7">
-        <v>3.69</v>
+        <v>1.32</v>
       </c>
       <c r="L7">
-        <v>0.6335158485101847</v>
+        <v>-0.8323433198102834</v>
       </c>
       <c r="M7">
-        <v>163.3319976806641</v>
+        <v>106.0499984741211</v>
       </c>
       <c r="N7">
-        <v>156.8389984130859</v>
+        <v>102.5409992218018</v>
       </c>
       <c r="O7">
-        <v>165.6498001098633</v>
+        <v>97.0247996520996</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7">
-        <v>163.32244972229</v>
+        <v>77.24449974060059</v>
       </c>
       <c r="R7">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="S7">
-        <v>0.95</v>
+        <v>1.06</v>
       </c>
       <c r="U7">
         <v>0</v>
@@ -1525,61 +1543,61 @@
         <v>1</v>
       </c>
       <c r="X7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>107.25</v>
+        <v>54.77</v>
       </c>
       <c r="Z7">
-        <v>207.73</v>
+        <v>108.85</v>
       </c>
       <c r="AA7">
-        <v>21.25</v>
+        <v>132.63</v>
       </c>
       <c r="AB7">
-        <v>18.87</v>
+        <v>15.39</v>
       </c>
       <c r="AC7">
-        <v>15.67</v>
+        <v>59.76</v>
       </c>
       <c r="AD7">
-        <v>141.1</v>
+        <v>106.75</v>
       </c>
       <c r="AE7">
-        <v>79.84</v>
-      </c>
-      <c r="AF7">
-        <v>-58.71</v>
-      </c>
-      <c r="AG7">
-        <v>80.81999999999999</v>
-      </c>
-      <c r="AH7">
-        <v>394.95</v>
+        <v>31.02</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>72</v>
       </c>
       <c r="AI7" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="AJ7" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AK7" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="AL7" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="AM7">
-        <v>8.94</v>
+        <v>2.51</v>
       </c>
       <c r="AN7">
-        <v>14.36</v>
+        <v>2.16</v>
       </c>
       <c r="AO7">
-        <v>60.63</v>
+        <v>-13.94</v>
       </c>
       <c r="AP7">
-        <v>36.78150075927504</v>
+        <v>50.60665630052341</v>
       </c>
     </row>
     <row r="8" spans="1:42">
@@ -1587,64 +1605,61 @@
         <v>48</v>
       </c>
       <c r="B8">
-        <v>95.22862823061629</v>
+        <v>97.21669980119285</v>
       </c>
       <c r="C8">
-        <v>98.60834990059642</v>
+        <v>95.62624254473161</v>
       </c>
       <c r="D8">
-        <v>222</v>
+        <v>35</v>
       </c>
       <c r="E8">
-        <v>266</v>
+        <v>36</v>
       </c>
       <c r="F8">
-        <v>153.48</v>
+        <v>297.72</v>
       </c>
       <c r="G8">
-        <v>0.5017805104646846</v>
+        <v>0.7341089205203364</v>
       </c>
       <c r="H8">
-        <v>0.4383389742069345</v>
+        <v>1.974214389693718</v>
       </c>
       <c r="I8">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="J8">
-        <v>-1.069351779716717</v>
+        <v>-0.07355267331234096</v>
       </c>
       <c r="K8">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="L8">
-        <v>-1.198443834492491</v>
+        <v>0.2493453284637314</v>
       </c>
       <c r="M8">
-        <v>150.4440002441406</v>
+        <v>296.0200073242187</v>
       </c>
       <c r="N8">
-        <v>138.673999786377</v>
+        <v>285.5199996948242</v>
       </c>
       <c r="O8">
-        <v>133.716199798584</v>
+        <v>266.6587991333008</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8">
-        <v>120.1982998657227</v>
+        <v>215.0780995178223</v>
       </c>
       <c r="R8">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="S8">
-        <v>1.04</v>
-      </c>
-      <c r="T8" t="s">
-        <v>66</v>
+        <v>1.07</v>
       </c>
       <c r="U8">
-        <v>3.888888888888888</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="V8" t="b">
         <v>0</v>
@@ -1656,55 +1671,58 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>93.17</v>
+        <v>128.5</v>
       </c>
       <c r="Z8">
-        <v>153.74</v>
+        <v>306.95</v>
       </c>
       <c r="AA8">
-        <v>36.63</v>
+        <v>1400.32</v>
       </c>
       <c r="AB8">
-        <v>-5.3</v>
+        <v>13.91</v>
       </c>
       <c r="AC8">
-        <v>7.68</v>
+        <v>35.81</v>
       </c>
       <c r="AD8">
-        <v>99.37</v>
+        <v>132.81</v>
+      </c>
+      <c r="AE8">
+        <v>18.98</v>
       </c>
       <c r="AF8">
-        <v>27.88</v>
+        <v>26.62</v>
       </c>
       <c r="AG8">
-        <v>-3.51</v>
+        <v>331</v>
       </c>
       <c r="AH8">
-        <v>76.29000000000001</v>
+        <v>-187.72</v>
       </c>
       <c r="AI8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AJ8" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="AK8" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="AL8" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="AM8">
-        <v>6.38</v>
+        <v>2.74</v>
       </c>
       <c r="AN8">
-        <v>8.640000000000001</v>
+        <v>6.17</v>
       </c>
       <c r="AO8">
-        <v>35.42</v>
+        <v>125.18</v>
       </c>
       <c r="AP8">
-        <v>31.82717237284929</v>
+        <v>48.74853283919893</v>
       </c>
     </row>
     <row r="9" spans="1:42">
@@ -1712,64 +1730,61 @@
         <v>49</v>
       </c>
       <c r="B9">
-        <v>99.40357852882704</v>
+        <v>95.62624254473161</v>
       </c>
       <c r="C9">
-        <v>92.04771371769384</v>
+        <v>91.45129224652088</v>
       </c>
       <c r="D9">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="E9">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="F9">
-        <v>1155.41</v>
+        <v>276.23</v>
       </c>
       <c r="G9">
-        <v>0.8463354954356865</v>
+        <v>0.4443075659734406</v>
       </c>
       <c r="H9">
-        <v>1.037878625299096</v>
+        <v>1.157402813382711</v>
       </c>
       <c r="I9">
-        <v>2.64</v>
+        <v>1.31</v>
       </c>
       <c r="J9">
-        <v>-0.2337840474687382</v>
+        <v>-0.7748219969478117</v>
       </c>
       <c r="K9">
-        <v>2.77</v>
+        <v>1.48</v>
       </c>
       <c r="L9">
-        <v>-0.1467632757316957</v>
+        <v>-0.5952608763529651</v>
       </c>
       <c r="M9">
-        <v>1143.423999023438</v>
+        <v>272.1099975585938</v>
       </c>
       <c r="N9">
-        <v>1049.412496948242</v>
+        <v>263.8954978942871</v>
       </c>
       <c r="O9">
-        <v>981.0983984375</v>
+        <v>252.6599993896484</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9">
-        <v>847.9501971435546</v>
+        <v>206.0913499450684</v>
       </c>
       <c r="R9">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="S9">
-        <v>1.07</v>
-      </c>
-      <c r="T9" t="s">
-        <v>66</v>
+        <v>1.04</v>
       </c>
       <c r="U9">
-        <v>8.333333333333332</v>
+        <v>17.22222222222222</v>
       </c>
       <c r="V9" t="b">
         <v>0</v>
@@ -1781,58 +1796,58 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>580.25</v>
+        <v>150.2</v>
       </c>
       <c r="Z9">
-        <v>1164</v>
+        <v>276.85</v>
       </c>
       <c r="AA9">
-        <v>491.71</v>
+        <v>292.93</v>
       </c>
       <c r="AB9">
-        <v>36.85</v>
+        <v>94.19</v>
       </c>
       <c r="AC9">
-        <v>29.03</v>
+        <v>27.61</v>
       </c>
       <c r="AD9">
-        <v>25.26</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="AE9">
-        <v>40.84</v>
+        <v>40.2</v>
       </c>
       <c r="AF9">
-        <v>-20.83</v>
+        <v>5.11</v>
       </c>
       <c r="AG9">
-        <v>10.62</v>
+        <v>2.92</v>
       </c>
       <c r="AH9">
-        <v>-7.59</v>
+        <v>47.41</v>
       </c>
       <c r="AI9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AJ9" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AK9" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="AL9" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="AM9">
-        <v>21.14</v>
+        <v>7</v>
       </c>
       <c r="AN9">
-        <v>23.78</v>
+        <v>5.24</v>
       </c>
       <c r="AO9">
-        <v>12.49</v>
+        <v>-25.14</v>
       </c>
       <c r="AP9">
-        <v>31.45023769165746</v>
+        <v>48.4343147987075</v>
       </c>
     </row>
     <row r="10" spans="1:42">
@@ -1840,64 +1855,64 @@
         <v>50</v>
       </c>
       <c r="B10">
-        <v>99.20477137176938</v>
+        <v>95.22862823061629</v>
       </c>
       <c r="C10">
-        <v>98.80715705765407</v>
+        <v>60.63618290258449</v>
       </c>
       <c r="D10">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="E10">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="F10">
-        <v>157.12</v>
+        <v>91.62</v>
       </c>
       <c r="G10">
-        <v>0.8502506751305431</v>
+        <v>0.4404231258860833</v>
       </c>
       <c r="H10">
-        <v>1.392804779489653</v>
+        <v>0.3496637848766043</v>
       </c>
       <c r="I10">
-        <v>3.44</v>
+        <v>1.08</v>
       </c>
       <c r="J10">
-        <v>0.3851550134556906</v>
+        <v>-1.110846881189808</v>
       </c>
       <c r="K10">
-        <v>3.31</v>
+        <v>1.14</v>
       </c>
       <c r="L10">
-        <v>0.3112266450189733</v>
+        <v>-1.099061068699767</v>
       </c>
       <c r="M10">
-        <v>153.8720001220703</v>
+        <v>89.84999999999999</v>
       </c>
       <c r="N10">
-        <v>135.0775005340576</v>
+        <v>86.11650085449219</v>
       </c>
       <c r="O10">
-        <v>131.0208001708984</v>
+        <v>83.75100051879883</v>
       </c>
       <c r="P10" t="b">
         <v>1</v>
       </c>
       <c r="Q10">
-        <v>113.670950088501</v>
+        <v>80.37125</v>
       </c>
       <c r="R10">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="S10">
         <v>1.03</v>
       </c>
       <c r="T10" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="U10">
-        <v>1.111111111111111</v>
+        <v>5</v>
       </c>
       <c r="V10" t="b">
         <v>0</v>
@@ -1909,58 +1924,58 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>76.83</v>
+        <v>57.58</v>
       </c>
       <c r="Z10">
-        <v>157.43</v>
+        <v>91.89</v>
       </c>
       <c r="AA10">
-        <v>63.43</v>
+        <v>40.9</v>
       </c>
       <c r="AB10">
-        <v>22.24</v>
+        <v>-4.94</v>
       </c>
       <c r="AC10">
-        <v>27.73</v>
+        <v>6.33</v>
       </c>
       <c r="AD10">
-        <v>43.48</v>
+        <v>820.16</v>
       </c>
       <c r="AE10">
-        <v>28.29</v>
+        <v>11.32</v>
       </c>
       <c r="AF10">
-        <v>-4.94</v>
+        <v>25.37</v>
       </c>
       <c r="AG10">
-        <v>24.62</v>
+        <v>-55.48</v>
       </c>
       <c r="AH10">
-        <v>10.17</v>
+        <v>1208.7</v>
       </c>
       <c r="AI10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AJ10" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AK10" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="AL10" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="AM10">
-        <v>3.06</v>
+        <v>4.03</v>
       </c>
       <c r="AN10">
-        <v>3.17</v>
+        <v>7.74</v>
       </c>
       <c r="AO10">
-        <v>3.59</v>
+        <v>92.06</v>
       </c>
       <c r="AP10">
-        <v>31.27138628379833</v>
+        <v>47.75691183160053</v>
       </c>
     </row>
     <row r="11" spans="1:42">
@@ -1968,61 +1983,61 @@
         <v>51</v>
       </c>
       <c r="B11">
-        <v>96.02385685884693</v>
+        <v>92.04771371769384</v>
       </c>
       <c r="C11">
-        <v>82.10735586481114</v>
+        <v>74.15506958250498</v>
       </c>
       <c r="D11">
-        <v>232</v>
+        <v>93</v>
       </c>
       <c r="E11">
-        <v>256</v>
+        <v>76</v>
       </c>
       <c r="F11">
-        <v>151.34</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="G11">
-        <v>0.5126673234164445</v>
+        <v>0.3817401319584383</v>
       </c>
       <c r="H11">
-        <v>0.3701527556389083</v>
+        <v>0.8501009381096333</v>
       </c>
       <c r="I11">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="J11">
-        <v>-1.224086544947825</v>
+        <v>-0.8770904399779846</v>
       </c>
       <c r="K11">
-        <v>1.66</v>
+        <v>0.95</v>
       </c>
       <c r="L11">
-        <v>-1.088187001719182</v>
+        <v>-1.380596470305332</v>
       </c>
       <c r="M11">
-        <v>150.7639984130859</v>
+        <v>97.36800079345703</v>
       </c>
       <c r="N11">
-        <v>147.5624992370605</v>
+        <v>94.94250030517578</v>
       </c>
       <c r="O11">
-        <v>148.6123989868164</v>
+        <v>91.35920013427734</v>
       </c>
       <c r="P11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11">
-        <v>133.8559495162964</v>
+        <v>81.5074002456665</v>
       </c>
       <c r="R11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="S11">
-        <v>0.99</v>
+        <v>1.04</v>
       </c>
       <c r="U11">
-        <v>0.5555555555555555</v>
+        <v>5.555555555555555</v>
       </c>
       <c r="V11" t="b">
         <v>1</v>
@@ -2031,61 +2046,61 @@
         <v>1</v>
       </c>
       <c r="X11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11">
-        <v>95.86</v>
+        <v>61.15</v>
       </c>
       <c r="Z11">
-        <v>158.55</v>
+        <v>99.59</v>
       </c>
       <c r="AA11">
-        <v>98.97</v>
+        <v>176.43</v>
       </c>
       <c r="AB11">
-        <v>-7.23</v>
+        <v>2.26</v>
       </c>
       <c r="AC11">
-        <v>19.31</v>
+        <v>42.72</v>
       </c>
       <c r="AD11">
-        <v>49.86</v>
+        <v>64.33</v>
       </c>
       <c r="AE11">
-        <v>3.52</v>
-      </c>
-      <c r="AF11">
-        <v>-72.97</v>
-      </c>
-      <c r="AG11">
-        <v>76.19</v>
-      </c>
-      <c r="AH11">
-        <v>90.91</v>
+        <v>15.59</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>72</v>
       </c>
       <c r="AI11" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ11" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="AK11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="AL11" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="AM11">
-        <v>1.76</v>
+        <v>3.72</v>
       </c>
       <c r="AN11">
-        <v>1.82</v>
+        <v>3.8</v>
       </c>
       <c r="AO11">
-        <v>3.41</v>
+        <v>2.15</v>
       </c>
       <c r="AP11">
-        <v>29.75676383737215</v>
+        <v>46.44372043783023</v>
       </c>
     </row>
     <row r="12" spans="1:42">
@@ -2093,64 +2108,61 @@
         <v>52</v>
       </c>
       <c r="B12">
-        <v>94.83101391650099</v>
+        <v>100</v>
       </c>
       <c r="C12">
-        <v>92.6441351888668</v>
+        <v>95.82504970178927</v>
       </c>
       <c r="D12">
-        <v>256</v>
+        <v>9</v>
       </c>
       <c r="E12">
-        <v>288</v>
+        <v>7</v>
       </c>
       <c r="F12">
-        <v>118.67</v>
+        <v>160.66</v>
       </c>
       <c r="G12">
-        <v>0.4051373165167173</v>
+        <v>4.844960100086917</v>
       </c>
       <c r="H12">
-        <v>1.552226678365347</v>
+        <v>2.158790738074851</v>
       </c>
       <c r="I12">
-        <v>3.76</v>
+        <v>2.04</v>
       </c>
       <c r="J12">
-        <v>0.632730637825462</v>
+        <v>0.2916917660811334</v>
       </c>
       <c r="K12">
-        <v>4.17</v>
+        <v>3.16</v>
       </c>
       <c r="L12">
-        <v>1.040618000288557</v>
+        <v>1.894104779948878</v>
       </c>
       <c r="M12">
-        <v>116.5380004882813</v>
+        <v>157.6260040283203</v>
       </c>
       <c r="N12">
-        <v>104.6630001068115</v>
+        <v>151.9375030517578</v>
       </c>
       <c r="O12">
-        <v>99.54579986572266</v>
+        <v>140.6562007141113</v>
       </c>
       <c r="P12" t="b">
         <v>1</v>
       </c>
       <c r="Q12">
-        <v>93.24840015411377</v>
+        <v>97.1819501876831</v>
       </c>
       <c r="R12">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="S12">
-        <v>1.05</v>
-      </c>
-      <c r="T12" t="s">
-        <v>19</v>
+        <v>1.08</v>
       </c>
       <c r="U12">
-        <v>7.222222222222223</v>
+        <v>0</v>
       </c>
       <c r="V12" t="b">
         <v>0</v>
@@ -2162,58 +2174,58 @@
         <v>0</v>
       </c>
       <c r="Y12">
-        <v>65.11</v>
+        <v>21.23</v>
       </c>
       <c r="Z12">
-        <v>119.82</v>
+        <v>161.4</v>
       </c>
       <c r="AA12">
-        <v>24.17</v>
+        <v>379.14</v>
       </c>
       <c r="AB12">
-        <v>-20.43</v>
+        <v>-73.95999999999999</v>
       </c>
       <c r="AC12">
-        <v>9.81</v>
+        <v>41.69</v>
       </c>
       <c r="AD12">
-        <v>41</v>
+        <v>90.45</v>
       </c>
       <c r="AE12">
-        <v>41.79</v>
+        <v>12.41</v>
       </c>
       <c r="AF12">
-        <v>181.79</v>
+        <v>125</v>
       </c>
       <c r="AG12">
-        <v>-209.22</v>
+        <v>-33.33</v>
       </c>
       <c r="AH12">
-        <v>47.03</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="AJ12" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="AK12" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="AL12" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="AM12">
-        <v>4.98</v>
+        <v>0.23</v>
       </c>
       <c r="AN12">
-        <v>6.9</v>
+        <v>0.47</v>
       </c>
       <c r="AO12">
-        <v>38.55</v>
+        <v>104.35</v>
       </c>
       <c r="AP12">
-        <v>27.93484415832933</v>
+        <v>45.89681882530785</v>
       </c>
     </row>
     <row r="13" spans="1:42">
@@ -2221,124 +2233,124 @@
         <v>53</v>
       </c>
       <c r="B13">
-        <v>91.25248508946322</v>
+        <v>93.63817097415506</v>
       </c>
       <c r="C13">
-        <v>61.82902584493042</v>
+        <v>65.8051689860835</v>
       </c>
       <c r="D13">
-        <v>110</v>
+        <v>244</v>
       </c>
       <c r="E13">
-        <v>91</v>
+        <v>277</v>
       </c>
       <c r="F13">
-        <v>104.8</v>
+        <v>168.78</v>
       </c>
       <c r="G13">
-        <v>0.3713007562549507</v>
+        <v>0.4261688516326759</v>
       </c>
       <c r="H13">
-        <v>0.7587248500409577</v>
+        <v>0.3447678786705934</v>
       </c>
       <c r="I13">
-        <v>2.14</v>
+        <v>1.42</v>
       </c>
       <c r="J13">
-        <v>-0.6206209605465063</v>
+        <v>-0.6141144436146831</v>
       </c>
       <c r="K13">
-        <v>2.19</v>
+        <v>1.33</v>
       </c>
       <c r="L13">
-        <v>-0.6386783757972291</v>
+        <v>-0.8175256670942009</v>
       </c>
       <c r="M13">
-        <v>104.2560012817383</v>
+        <v>166.4860046386719</v>
       </c>
       <c r="N13">
-        <v>99.0805004119873</v>
+        <v>159.8810020446777</v>
       </c>
       <c r="O13">
-        <v>99.22660034179688</v>
+        <v>155.3048004150391</v>
       </c>
       <c r="P13" t="b">
         <v>1</v>
       </c>
       <c r="Q13">
-        <v>90.98799991607666</v>
+        <v>143.830849647522</v>
       </c>
       <c r="R13">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="S13">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="U13">
-        <v>2.222222222222222</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="V13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="b">
         <v>1</v>
       </c>
       <c r="X13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y13">
-        <v>71.88</v>
+        <v>110.74</v>
       </c>
       <c r="Z13">
-        <v>107.17</v>
+        <v>169</v>
       </c>
       <c r="AA13">
-        <v>155.05</v>
+        <v>112.88</v>
       </c>
       <c r="AB13">
-        <v>-17.84</v>
+        <v>-7.23</v>
       </c>
       <c r="AC13">
-        <v>16.24</v>
+        <v>18.83</v>
       </c>
       <c r="AD13">
-        <v>35.11</v>
+        <v>193.04</v>
       </c>
       <c r="AE13">
-        <v>9.65</v>
+        <v>3.48</v>
       </c>
       <c r="AF13">
-        <v>18.75</v>
+        <v>100</v>
       </c>
       <c r="AG13">
-        <v>45.45</v>
+        <v>-72.97</v>
       </c>
       <c r="AH13">
-        <v>-35.29</v>
+        <v>76.19</v>
       </c>
       <c r="AI13" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="AJ13" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="AK13" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="AL13" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="AM13">
-        <v>1.37</v>
+        <v>1.8</v>
       </c>
       <c r="AN13">
-        <v>2.79</v>
+        <v>1.82</v>
       </c>
       <c r="AO13">
-        <v>103.65</v>
+        <v>1.11</v>
       </c>
       <c r="AP13">
-        <v>26.7719007974712</v>
+        <v>45.76654392567536</v>
       </c>
     </row>
     <row r="14" spans="1:42">
@@ -2346,61 +2358,61 @@
         <v>54</v>
       </c>
       <c r="B14">
-        <v>98.80715705765407</v>
+        <v>97.81312127236581</v>
       </c>
       <c r="C14">
-        <v>33.99602385685885</v>
+        <v>72.96222664015905</v>
       </c>
       <c r="D14">
-        <v>466</v>
+        <v>179</v>
       </c>
       <c r="E14">
-        <v>478</v>
+        <v>232</v>
       </c>
       <c r="F14">
-        <v>601.8200000000001</v>
+        <v>181.16</v>
       </c>
       <c r="G14">
-        <v>0.7387936242899842</v>
+        <v>0.7063326577961705</v>
       </c>
       <c r="H14">
-        <v>1.194421800102236</v>
+        <v>1.310695323314143</v>
       </c>
       <c r="I14">
-        <v>3.1</v>
+        <v>2.11</v>
       </c>
       <c r="J14">
-        <v>0.1221059125628084</v>
+        <v>0.393960209111306</v>
       </c>
       <c r="K14">
-        <v>4.54</v>
+        <v>1.74</v>
       </c>
       <c r="L14">
-        <v>1.354425908951053</v>
+        <v>-0.2100019057348227</v>
       </c>
       <c r="M14">
-        <v>614.8299926757812</v>
+        <v>185.3</v>
       </c>
       <c r="N14">
-        <v>586.677001953125</v>
+        <v>185.013500213623</v>
       </c>
       <c r="O14">
-        <v>558.1998040771484</v>
+        <v>178.1963998413086</v>
       </c>
       <c r="P14" t="b">
         <v>1</v>
       </c>
       <c r="Q14">
-        <v>513.2698013305665</v>
+        <v>137.7923002624512</v>
       </c>
       <c r="R14">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="S14">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="V14" t="b">
         <v>0</v>
@@ -2412,58 +2424,58 @@
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>273.52</v>
+        <v>85.39</v>
       </c>
       <c r="Z14">
-        <v>715.99</v>
+        <v>193.26</v>
       </c>
       <c r="AA14">
-        <v>46.85</v>
+        <v>73.03</v>
       </c>
       <c r="AB14">
-        <v>218.25</v>
+        <v>22.24</v>
       </c>
       <c r="AC14">
-        <v>2.85</v>
+        <v>33.4</v>
       </c>
       <c r="AD14">
-        <v>122.28</v>
+        <v>54.9</v>
       </c>
       <c r="AE14">
-        <v>19.1</v>
+        <v>29.98</v>
       </c>
       <c r="AF14">
-        <v>100</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="AG14">
-        <v>64.81</v>
+        <v>-3.7</v>
       </c>
       <c r="AH14">
-        <v>-69.48999999999999</v>
+        <v>24.62</v>
       </c>
       <c r="AI14" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="AJ14" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AK14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="AL14" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="AM14">
-        <v>4.81</v>
+        <v>3.43</v>
       </c>
       <c r="AN14">
-        <v>6.2</v>
+        <v>3.17</v>
       </c>
       <c r="AO14">
-        <v>28.9</v>
+        <v>-7.58</v>
       </c>
       <c r="AP14">
-        <v>25.80815948402498</v>
+        <v>45.76526869039433</v>
       </c>
     </row>
     <row r="15" spans="1:42">
@@ -2471,127 +2483,124 @@
         <v>55</v>
       </c>
       <c r="B15">
-        <v>92.6441351888668</v>
+        <v>98.60834990059642</v>
       </c>
       <c r="C15">
-        <v>62.02783300198808</v>
+        <v>94.23459244532803</v>
       </c>
       <c r="D15">
-        <v>175</v>
+        <v>239</v>
       </c>
       <c r="E15">
-        <v>177</v>
+        <v>285</v>
       </c>
       <c r="F15">
-        <v>83.95</v>
+        <v>315.7</v>
       </c>
       <c r="G15">
-        <v>0.3790721207848676</v>
+        <v>0.882777801907348</v>
       </c>
       <c r="H15">
-        <v>0.9029483837698742</v>
+        <v>1.657280003620149</v>
       </c>
       <c r="I15">
-        <v>2.36</v>
+        <v>1.84</v>
       </c>
       <c r="J15">
-        <v>-0.4504127187922886</v>
+        <v>-0.0005037854336460265</v>
       </c>
       <c r="K15">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
       <c r="L15">
-        <v>-0.6217157861397969</v>
+        <v>0.3382512447602258</v>
       </c>
       <c r="M15">
-        <v>82.41800079345703</v>
+        <v>322.6679992675781</v>
       </c>
       <c r="N15">
-        <v>78.89450035095214</v>
+        <v>339.0075012207031</v>
       </c>
       <c r="O15">
-        <v>81.39699996948242</v>
+        <v>301.6552014160156</v>
       </c>
       <c r="P15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15">
-        <v>76.88149993896485</v>
+        <v>246.6988502502441</v>
       </c>
       <c r="R15">
-        <v>1.04</v>
+        <v>0.95</v>
       </c>
       <c r="S15">
-        <v>0.97</v>
-      </c>
-      <c r="T15" t="s">
-        <v>65</v>
+        <v>1.12</v>
       </c>
       <c r="U15">
-        <v>1.666666666666667</v>
+        <v>14.44444444444444</v>
       </c>
       <c r="V15" t="b">
         <v>0</v>
       </c>
       <c r="W15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X15" t="b">
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>56.98</v>
+        <v>130.08</v>
       </c>
       <c r="Z15">
-        <v>90.34</v>
+        <v>355.91</v>
       </c>
       <c r="AA15">
-        <v>60.06</v>
+        <v>85.75</v>
       </c>
       <c r="AB15">
-        <v>5.14</v>
+        <v>4.1</v>
       </c>
       <c r="AC15">
-        <v>16.24</v>
+        <v>32.21</v>
       </c>
       <c r="AD15">
-        <v>26.35</v>
+        <v>44.78</v>
       </c>
       <c r="AE15">
-        <v>11.29</v>
+        <v>47.48</v>
       </c>
       <c r="AF15">
-        <v>3.31</v>
+        <v>31.55</v>
       </c>
       <c r="AG15">
-        <v>-1.31</v>
+        <v>-51.18</v>
       </c>
       <c r="AH15">
-        <v>21.43</v>
+        <v>27.11</v>
       </c>
       <c r="AI15" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="AJ15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AK15" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="AL15" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="AM15">
-        <v>6.13</v>
+        <v>13.45</v>
       </c>
       <c r="AN15">
-        <v>6.53</v>
+        <v>14.29</v>
       </c>
       <c r="AO15">
-        <v>6.53</v>
+        <v>6.25</v>
       </c>
       <c r="AP15">
-        <v>24.09253533571355</v>
+        <v>45.62261841575108</v>
       </c>
     </row>
     <row r="16" spans="1:42">
@@ -2602,124 +2611,121 @@
         <v>98.40954274353876</v>
       </c>
       <c r="C16">
-        <v>97.61431411530815</v>
+        <v>96.02385685884693</v>
       </c>
       <c r="D16">
-        <v>141</v>
+        <v>405</v>
       </c>
       <c r="E16">
-        <v>108</v>
+        <v>392</v>
       </c>
       <c r="F16">
-        <v>175.36</v>
+        <v>222.29</v>
       </c>
       <c r="G16">
-        <v>0.7596854874806023</v>
+        <v>0.8253202836857648</v>
       </c>
       <c r="H16">
-        <v>0.1720636975825572</v>
+        <v>1.392484701089993</v>
       </c>
       <c r="I16">
-        <v>0.98</v>
+        <v>1.89</v>
       </c>
       <c r="J16">
-        <v>-1.518082598886928</v>
+        <v>0.07254510244504858</v>
       </c>
       <c r="K16">
-        <v>1.58</v>
+        <v>1.97</v>
       </c>
       <c r="L16">
-        <v>-1.156037360348911</v>
+        <v>0.1308041067350724</v>
       </c>
       <c r="M16">
-        <v>172.7080017089844</v>
+        <v>224.1639984130859</v>
       </c>
       <c r="N16">
-        <v>165.363500213623</v>
+        <v>222.4829986572266</v>
       </c>
       <c r="O16">
-        <v>158.4052001953125</v>
+        <v>203.3675997924805</v>
       </c>
       <c r="P16" t="b">
         <v>1</v>
       </c>
       <c r="Q16">
-        <v>133.9255002212524</v>
+        <v>158.94024974823</v>
       </c>
       <c r="R16">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="S16">
-        <v>1.04</v>
-      </c>
-      <c r="T16" t="s">
-        <v>66</v>
+        <v>1.09</v>
       </c>
       <c r="U16">
-        <v>2.777777777777778</v>
+        <v>19.44444444444445</v>
       </c>
       <c r="V16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X16" t="b">
         <v>1</v>
       </c>
       <c r="Y16">
-        <v>96.65000000000001</v>
+        <v>95.84999999999999</v>
       </c>
       <c r="Z16">
-        <v>176.49</v>
+        <v>232.84</v>
       </c>
       <c r="AA16">
-        <v>272.95</v>
+        <v>23.86</v>
       </c>
       <c r="AB16">
-        <v>-0.38</v>
+        <v>43.9</v>
       </c>
       <c r="AC16">
-        <v>13.38</v>
+        <v>10.37</v>
       </c>
       <c r="AD16">
-        <v>25.05</v>
+        <v>91.61</v>
       </c>
       <c r="AE16">
-        <v>4.92</v>
-      </c>
-      <c r="AF16">
-        <v>-118.69</v>
-      </c>
-      <c r="AG16">
-        <v>28.57</v>
-      </c>
-      <c r="AH16">
-        <v>11.59</v>
+        <v>32.41</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>72</v>
       </c>
       <c r="AI16" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="AJ16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AK16" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="AL16" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="AM16">
-        <v>6.35</v>
+        <v>5.25</v>
       </c>
       <c r="AN16">
-        <v>7.2</v>
+        <v>10.01</v>
       </c>
       <c r="AO16">
-        <v>13.39</v>
+        <v>90.67</v>
       </c>
       <c r="AP16">
-        <v>23.1382906885474</v>
+        <v>42.98989410785375</v>
       </c>
     </row>
     <row r="17" spans="1:42">
@@ -2727,55 +2733,55 @@
         <v>57</v>
       </c>
       <c r="B17">
-        <v>98.60834990059642</v>
+        <v>90.05964214711729</v>
       </c>
       <c r="C17">
-        <v>58.05168986083499</v>
+        <v>39.56262425447316</v>
       </c>
       <c r="D17">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E17">
-        <v>160</v>
+        <v>98</v>
       </c>
       <c r="F17">
-        <v>106.72</v>
+        <v>106.79</v>
       </c>
       <c r="G17">
-        <v>0.7243284025394569</v>
+        <v>0.2929148104563439</v>
       </c>
       <c r="H17">
-        <v>1.059065520330901</v>
+        <v>0.7408983949039637</v>
       </c>
       <c r="I17">
-        <v>3.58</v>
+        <v>1.37</v>
       </c>
       <c r="J17">
-        <v>0.4934693491174658</v>
+        <v>-0.6871633314933778</v>
       </c>
       <c r="K17">
-        <v>3</v>
+        <v>1.17</v>
       </c>
       <c r="L17">
-        <v>0.04830650532877438</v>
+        <v>-1.054608110551519</v>
       </c>
       <c r="M17">
-        <v>106.5880004882813</v>
+        <v>106.0700012207031</v>
       </c>
       <c r="N17">
-        <v>100.6195003509522</v>
+        <v>104.7480007171631</v>
       </c>
       <c r="O17">
-        <v>99.40880020141601</v>
+        <v>103.7568003845215</v>
       </c>
       <c r="P17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17">
-        <v>89.34295021057129</v>
+        <v>98.02835006713867</v>
       </c>
       <c r="R17">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="S17">
         <v>1.01</v>
@@ -2784,67 +2790,67 @@
         <v>0</v>
       </c>
       <c r="V17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" t="b">
         <v>1</v>
       </c>
       <c r="X17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17">
-        <v>54.57</v>
+        <v>71.88</v>
       </c>
       <c r="Z17">
-        <v>114.82</v>
+        <v>108.94</v>
       </c>
       <c r="AA17">
-        <v>82.06</v>
+        <v>158.24</v>
       </c>
       <c r="AB17">
-        <v>42.92</v>
+        <v>-17.84</v>
       </c>
       <c r="AC17">
-        <v>4.04</v>
+        <v>18.85</v>
       </c>
       <c r="AD17">
-        <v>68.59999999999999</v>
+        <v>144.43</v>
       </c>
       <c r="AE17">
-        <v>338.74</v>
-      </c>
-      <c r="AF17">
-        <v>-2.82</v>
-      </c>
-      <c r="AG17">
-        <v>42</v>
-      </c>
-      <c r="AH17">
-        <v>28.21</v>
+        <v>11.71</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>72</v>
       </c>
       <c r="AI17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ17" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="AK17" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="AL17" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="AM17">
-        <v>2.26</v>
+        <v>1.68</v>
       </c>
       <c r="AN17">
-        <v>2.41</v>
+        <v>2.79</v>
       </c>
       <c r="AO17">
-        <v>6.64</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="AP17">
-        <v>22.77730818442421</v>
+        <v>41.88053917296733</v>
       </c>
     </row>
     <row r="18" spans="1:42">
@@ -2852,61 +2858,61 @@
         <v>58</v>
       </c>
       <c r="B18">
-        <v>97.61431411530815</v>
+        <v>94.03578528827038</v>
       </c>
       <c r="C18">
-        <v>99.80119284294234</v>
+        <v>97.81312127236581</v>
       </c>
       <c r="D18">
-        <v>391</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>429</v>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>287.38</v>
+        <v>180</v>
       </c>
       <c r="G18">
-        <v>0.6423455994520519</v>
+        <v>0.3441777222523034</v>
       </c>
       <c r="H18">
-        <v>0.5096844038679891</v>
+        <v>2.07334342723443</v>
       </c>
       <c r="I18">
-        <v>2.18</v>
+        <v>1.73</v>
       </c>
       <c r="J18">
-        <v>-0.5896740075002849</v>
+        <v>-0.1612113387667749</v>
       </c>
       <c r="K18">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="L18">
-        <v>-1.003374053432021</v>
+        <v>0.1011688013029076</v>
       </c>
       <c r="M18">
-        <v>283.7880004882812</v>
+        <v>177.2739990234375</v>
       </c>
       <c r="N18">
-        <v>262.3224990844727</v>
+        <v>171.1500007629394</v>
       </c>
       <c r="O18">
-        <v>250.4066000366211</v>
+        <v>155.4756008911133</v>
       </c>
       <c r="P18" t="b">
         <v>1</v>
       </c>
       <c r="Q18">
-        <v>207.3934004211426</v>
+        <v>134.9744499206543</v>
       </c>
       <c r="R18">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="S18">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="U18">
-        <v>16.66666666666666</v>
+        <v>4.444444444444444</v>
       </c>
       <c r="V18" t="b">
         <v>0</v>
@@ -2915,61 +2921,61 @@
         <v>1</v>
       </c>
       <c r="X18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18">
-        <v>167.8</v>
+        <v>86.62</v>
       </c>
       <c r="Z18">
-        <v>288.95</v>
+        <v>183.3</v>
       </c>
       <c r="AA18">
-        <v>26.98</v>
+        <v>4389.77</v>
       </c>
       <c r="AB18">
-        <v>9.220000000000001</v>
+        <v>91.83</v>
       </c>
       <c r="AC18">
-        <v>9.82</v>
+        <v>45.8</v>
       </c>
       <c r="AD18">
-        <v>9.279999999999999</v>
+        <v>27.6</v>
       </c>
       <c r="AE18">
-        <v>-9.779999999999999</v>
-      </c>
-      <c r="AF18">
-        <v>-3.38</v>
-      </c>
-      <c r="AG18">
-        <v>2.99</v>
-      </c>
-      <c r="AH18">
-        <v>4.15</v>
+        <v>115.46</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>72</v>
       </c>
       <c r="AI18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AJ18" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="AK18" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="AL18" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="AM18">
-        <v>8.19</v>
+        <v>3.09</v>
       </c>
       <c r="AN18">
-        <v>8.65</v>
+        <v>4.12</v>
       </c>
       <c r="AO18">
-        <v>5.62</v>
+        <v>33.33</v>
       </c>
       <c r="AP18">
-        <v>21.72382257203495</v>
+        <v>40.29200993898849</v>
       </c>
     </row>
     <row r="19" spans="1:42">
@@ -2977,64 +2983,64 @@
         <v>59</v>
       </c>
       <c r="B19">
-        <v>90.65606361829026</v>
+        <v>99.60238568588468</v>
       </c>
       <c r="C19">
-        <v>83.30019880715706</v>
+        <v>97.21669980119285</v>
       </c>
       <c r="D19">
-        <v>134</v>
+        <v>186</v>
       </c>
       <c r="E19">
-        <v>150</v>
+        <v>182</v>
       </c>
       <c r="F19">
-        <v>40.48</v>
+        <v>111.89</v>
       </c>
       <c r="G19">
-        <v>0.3539826644431262</v>
+        <v>1.660236671369378</v>
       </c>
       <c r="H19">
-        <v>0.4130259021214583</v>
+        <v>1.269213361126383</v>
       </c>
       <c r="I19">
-        <v>1.46</v>
+        <v>1.94</v>
       </c>
       <c r="J19">
-        <v>-1.146719162332271</v>
+        <v>0.1455939903237435</v>
       </c>
       <c r="K19">
-        <v>1.51</v>
+        <v>2.19</v>
       </c>
       <c r="L19">
-        <v>-1.215406424149923</v>
+        <v>0.4567924664888851</v>
       </c>
       <c r="M19">
-        <v>39.48199996948242</v>
+        <v>108.365998840332</v>
       </c>
       <c r="N19">
-        <v>39.15850028991699</v>
+        <v>104.1919994354248</v>
       </c>
       <c r="O19">
-        <v>39.28360015869141</v>
+        <v>91.30080001831055</v>
       </c>
       <c r="P19" t="b">
         <v>1</v>
       </c>
       <c r="Q19">
-        <v>36.27095005989074</v>
+        <v>73.57024995803833</v>
       </c>
       <c r="R19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="S19">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="U19">
-        <v>2.222222222222222</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="V19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="b">
         <v>1</v>
@@ -3043,58 +3049,58 @@
         <v>0</v>
       </c>
       <c r="Y19">
-        <v>27.6</v>
+        <v>35.23</v>
       </c>
       <c r="Z19">
-        <v>41.45</v>
+        <v>111.93</v>
       </c>
       <c r="AA19">
-        <v>19.05</v>
+        <v>23.24</v>
       </c>
       <c r="AB19">
-        <v>13.16</v>
+        <v>9.6</v>
       </c>
       <c r="AC19">
-        <v>6.79</v>
+        <v>18.47</v>
       </c>
       <c r="AD19">
-        <v>30.95</v>
+        <v>59.68</v>
       </c>
       <c r="AE19">
-        <v>10.34</v>
+        <v>40.27</v>
       </c>
       <c r="AF19">
-        <v>152.63</v>
+        <v>-30.5</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="AH19">
-        <v>-75.31999999999999</v>
+        <v>17.39</v>
       </c>
       <c r="AI19" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AJ19" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AK19" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="AL19" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="AM19">
-        <v>1.85</v>
+        <v>3.8</v>
       </c>
       <c r="AN19">
-        <v>1.86</v>
+        <v>4.76</v>
       </c>
       <c r="AO19">
-        <v>0.54</v>
+        <v>25.26</v>
       </c>
       <c r="AP19">
-        <v>20.44060056922125</v>
+        <v>39.36352837455045</v>
       </c>
     </row>
     <row r="20" spans="1:42">
@@ -3102,64 +3108,64 @@
         <v>60</v>
       </c>
       <c r="B20">
+        <v>98.80715705765407</v>
+      </c>
+      <c r="C20">
         <v>96.81908548707754</v>
       </c>
-      <c r="C20">
-        <v>25.84493041749503</v>
-      </c>
       <c r="D20">
-        <v>480</v>
+        <v>266</v>
       </c>
       <c r="E20">
-        <v>472</v>
+        <v>251</v>
       </c>
       <c r="F20">
-        <v>267.48</v>
+        <v>173.91</v>
       </c>
       <c r="G20">
-        <v>0.4988361415327089</v>
+        <v>1.111101960988091</v>
       </c>
       <c r="H20">
-        <v>1.015179175067111</v>
+        <v>1.702575489006807</v>
       </c>
       <c r="I20">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="J20">
-        <v>-0.187363617899406</v>
+        <v>0.5984970951716518</v>
       </c>
       <c r="K20">
-        <v>2.31</v>
+        <v>3.87</v>
       </c>
       <c r="L20">
-        <v>-0.5369028378526359</v>
+        <v>2.946158122790728</v>
       </c>
       <c r="M20">
-        <v>266.8140014648437</v>
+        <v>167.0399993896484</v>
       </c>
       <c r="N20">
-        <v>262.8725006103516</v>
+        <v>156.0365005493164</v>
       </c>
       <c r="O20">
-        <v>266.6029992675781</v>
+        <v>155.6898001098633</v>
       </c>
       <c r="P20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20">
-        <v>244.059700088501</v>
+        <v>114.9852002716064</v>
       </c>
       <c r="R20">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="S20">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="V20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W20" t="b">
         <v>1</v>
@@ -3168,58 +3174,58 @@
         <v>1</v>
       </c>
       <c r="Y20">
-        <v>164.45</v>
+        <v>65.11</v>
       </c>
       <c r="Z20">
-        <v>313</v>
+        <v>174.45</v>
       </c>
       <c r="AA20">
-        <v>15.36</v>
+        <v>34</v>
       </c>
       <c r="AB20">
-        <v>6.18</v>
+        <v>-20.43</v>
       </c>
       <c r="AC20">
-        <v>9.25</v>
+        <v>13.96</v>
       </c>
       <c r="AD20">
-        <v>23.97</v>
+        <v>56.42</v>
       </c>
       <c r="AE20">
-        <v>19.89</v>
+        <v>44.91</v>
       </c>
       <c r="AF20">
-        <v>0.71</v>
+        <v>19.35</v>
       </c>
       <c r="AG20">
-        <v>15.04</v>
+        <v>181.79</v>
       </c>
       <c r="AH20">
-        <v>21.78</v>
+        <v>-209.22</v>
       </c>
       <c r="AI20" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AJ20" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="AK20" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="AL20" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="AM20">
-        <v>10.54</v>
+        <v>6.29</v>
       </c>
       <c r="AN20">
-        <v>15.4</v>
+        <v>6.9</v>
       </c>
       <c r="AO20">
-        <v>46.11</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AP20">
-        <v>18.8562252285294</v>
+        <v>38.35613432324472</v>
       </c>
     </row>
     <row r="21" spans="1:42">
@@ -3227,64 +3233,64 @@
         <v>61</v>
       </c>
       <c r="B21">
-        <v>91.65009940357854</v>
+        <v>94.43339960238568</v>
       </c>
       <c r="C21">
-        <v>35.58648111332008</v>
+        <v>80.91451292246521</v>
       </c>
       <c r="D21">
-        <v>455</v>
+        <v>232</v>
       </c>
       <c r="E21">
-        <v>441</v>
+        <v>165</v>
       </c>
       <c r="F21">
-        <v>240.37</v>
+        <v>101.41</v>
       </c>
       <c r="G21">
-        <v>0.3350331468756306</v>
+        <v>0.4163291625896793</v>
       </c>
       <c r="H21">
-        <v>1.356015194262818</v>
+        <v>0.9269770524628345</v>
       </c>
       <c r="I21">
-        <v>3.72</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J21">
-        <v>0.6017836847792409</v>
+        <v>-1.315383767250154</v>
       </c>
       <c r="K21">
-        <v>3.79</v>
+        <v>1.03</v>
       </c>
       <c r="L21">
-        <v>0.7183287967973456</v>
+        <v>-1.262055248576673</v>
       </c>
       <c r="M21">
-        <v>234.5019989013672</v>
+        <v>101.368000793457</v>
       </c>
       <c r="N21">
-        <v>216.2074981689453</v>
+        <v>98.06350021362304</v>
       </c>
       <c r="O21">
-        <v>223.8027993774414</v>
+        <v>93.29440002441406</v>
       </c>
       <c r="P21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21">
-        <v>213.5877000427246</v>
+        <v>84.26920013427734</v>
       </c>
       <c r="R21">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="S21">
-        <v>0.97</v>
+        <v>1.05</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>12.77777777777778</v>
       </c>
       <c r="V21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21" t="b">
         <v>1</v>
@@ -3293,58 +3299,58 @@
         <v>1</v>
       </c>
       <c r="Y21">
-        <v>155.96</v>
+        <v>60.93</v>
       </c>
       <c r="Z21">
-        <v>289.33</v>
+        <v>103.16</v>
       </c>
       <c r="AA21">
-        <v>14.85</v>
+        <v>71.52</v>
       </c>
       <c r="AB21">
-        <v>13</v>
+        <v>5.14</v>
       </c>
       <c r="AC21">
-        <v>17</v>
+        <v>21.9</v>
       </c>
       <c r="AD21">
-        <v>11.23</v>
+        <v>27.03</v>
       </c>
       <c r="AE21">
-        <v>27.57</v>
+        <v>11.75</v>
       </c>
       <c r="AF21">
-        <v>101.69</v>
+        <v>1.92</v>
       </c>
       <c r="AG21">
-        <v>-11.61</v>
+        <v>3.31</v>
       </c>
       <c r="AH21">
-        <v>89.36</v>
+        <v>-1.31</v>
       </c>
       <c r="AI21" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="AJ21" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="AK21" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="AL21" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="AM21">
-        <v>10.96</v>
+        <v>6.54</v>
       </c>
       <c r="AN21">
-        <v>13.02</v>
+        <v>6.53</v>
       </c>
       <c r="AO21">
-        <v>18.8</v>
+        <v>-0.15</v>
       </c>
       <c r="AP21">
-        <v>16.58476343806852</v>
+        <v>37.40091010811676</v>
       </c>
     </row>
     <row r="22" spans="1:42">
@@ -3352,121 +3358,124 @@
         <v>62</v>
       </c>
       <c r="B22">
-        <v>93.83697813121272</v>
+        <v>96.02385685884693</v>
       </c>
       <c r="C22">
-        <v>78.33001988071571</v>
+        <v>92.6441351888668</v>
       </c>
       <c r="D22">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E22">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="F22">
-        <v>58.94</v>
+        <v>92.86</v>
       </c>
       <c r="G22">
-        <v>0.436238978541</v>
+        <v>0.5524010351912558</v>
       </c>
       <c r="H22">
-        <v>0.7499695746373698</v>
+        <v>0.5223070943759024</v>
       </c>
       <c r="I22">
-        <v>1.97</v>
+        <v>4.27</v>
       </c>
       <c r="J22">
-        <v>-0.7521455109929476</v>
+        <v>3.549672165470924</v>
       </c>
       <c r="K22">
-        <v>2.07</v>
+        <v>2.62</v>
       </c>
       <c r="L22">
-        <v>-0.7404539137418223</v>
+        <v>1.093951533280429</v>
       </c>
       <c r="M22">
-        <v>59.32199935913086</v>
+        <v>86.48199920654297</v>
       </c>
       <c r="N22">
-        <v>58.3464994430542</v>
+        <v>80.53449974060058</v>
       </c>
       <c r="O22">
-        <v>57.94679969787597</v>
+        <v>77.64579971313476</v>
       </c>
       <c r="P22" t="b">
         <v>1</v>
       </c>
       <c r="Q22">
-        <v>53.05414999008179</v>
+        <v>68.55169992446899</v>
       </c>
       <c r="R22">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="S22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="V22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" t="b">
         <v>0</v>
       </c>
       <c r="Y22">
-        <v>38.63</v>
+        <v>53.74</v>
       </c>
       <c r="Z22">
-        <v>61.67</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="AA22">
-        <v>71.97</v>
+        <v>42.44</v>
       </c>
       <c r="AB22">
-        <v>21.1</v>
+        <v>13.57</v>
       </c>
       <c r="AC22">
         <v>11.61</v>
       </c>
       <c r="AD22">
-        <v>9.119999999999999</v>
+        <v>77.23</v>
       </c>
       <c r="AE22">
-        <v>18.32</v>
+        <v>42.63</v>
+      </c>
+      <c r="AF22">
+        <v>-21.74</v>
       </c>
       <c r="AG22">
-        <v>75.76000000000001</v>
+        <v>5.34</v>
       </c>
       <c r="AH22">
-        <v>-36.54</v>
+        <v>191.11</v>
       </c>
       <c r="AI22" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="AJ22" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="AK22" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="AL22" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="AM22">
-        <v>1.86</v>
+        <v>4.5</v>
       </c>
       <c r="AN22">
-        <v>2.09</v>
+        <v>5.22</v>
       </c>
       <c r="AO22">
-        <v>12.37</v>
+        <v>16</v>
       </c>
       <c r="AP22">
-        <v>12.61236659071334</v>
+        <v>33.87345068551772</v>
       </c>
     </row>
     <row r="23" spans="1:42">
@@ -3474,61 +3483,61 @@
         <v>63</v>
       </c>
       <c r="B23">
-        <v>93.63817097415506</v>
+        <v>95.82504970178927</v>
       </c>
       <c r="C23">
-        <v>97.01789264413519</v>
+        <v>89.06560636182903</v>
       </c>
       <c r="D23">
-        <v>365</v>
+        <v>27</v>
       </c>
       <c r="E23">
-        <v>369</v>
+        <v>53</v>
       </c>
       <c r="F23">
-        <v>404.14</v>
+        <v>776.37</v>
       </c>
       <c r="G23">
-        <v>0.4109169612590066</v>
+        <v>0.3473125484520636</v>
       </c>
       <c r="H23">
-        <v>0.838993674309928</v>
+        <v>1.380683308570984</v>
       </c>
       <c r="I23">
-        <v>3.64</v>
+        <v>2.95</v>
       </c>
       <c r="J23">
-        <v>0.539889778686798</v>
+        <v>1.62118152547338</v>
       </c>
       <c r="K23">
-        <v>2.82</v>
+        <v>2.29</v>
       </c>
       <c r="L23">
-        <v>-0.1043568015881154</v>
+        <v>0.6049689936497092</v>
       </c>
       <c r="M23">
-        <v>393.6780029296875</v>
+        <v>739.006005859375</v>
       </c>
       <c r="N23">
-        <v>359.7789978027344</v>
+        <v>720.4804992675781</v>
       </c>
       <c r="O23">
-        <v>361.4767980957031</v>
+        <v>701.8276013183594</v>
       </c>
       <c r="P23" t="b">
         <v>1</v>
       </c>
       <c r="Q23">
-        <v>355.5624488830566</v>
+        <v>630.035251159668</v>
       </c>
       <c r="R23">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="S23">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>3.888888888888888</v>
       </c>
       <c r="V23" t="b">
         <v>0</v>
@@ -3537,61 +3546,61 @@
         <v>1</v>
       </c>
       <c r="X23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y23">
-        <v>261.76</v>
+        <v>450.8</v>
       </c>
       <c r="Z23">
-        <v>415.27</v>
+        <v>784.75</v>
       </c>
       <c r="AA23">
-        <v>56.73</v>
+        <v>1950.35</v>
       </c>
       <c r="AB23">
-        <v>36.23</v>
+        <v>29.99</v>
       </c>
       <c r="AC23">
-        <v>6.7</v>
+        <v>16</v>
       </c>
       <c r="AD23">
-        <v>11.61</v>
+        <v>38.3</v>
       </c>
       <c r="AE23">
-        <v>36.94</v>
-      </c>
-      <c r="AF23">
-        <v>14.57</v>
-      </c>
-      <c r="AG23">
-        <v>4.78</v>
-      </c>
-      <c r="AH23">
-        <v>12.01</v>
+        <v>40.65</v>
+      </c>
+      <c r="AF23" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG23" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>72</v>
       </c>
       <c r="AI23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AJ23" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="AK23" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="AL23" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="AM23">
-        <v>35.85</v>
+        <v>27.53</v>
       </c>
       <c r="AN23">
-        <v>35.78</v>
+        <v>25.3</v>
       </c>
       <c r="AO23">
-        <v>-0.2</v>
+        <v>-8.1</v>
       </c>
       <c r="AP23">
-        <v>11.18007346322898</v>
+        <v>32.45821038795593</v>
       </c>
     </row>
     <row r="24" spans="1:42">
@@ -3599,64 +3608,64 @@
         <v>64</v>
       </c>
       <c r="B24">
-        <v>99.60238568588468</v>
+        <v>96.62027833001989</v>
       </c>
       <c r="C24">
-        <v>57.65407554671968</v>
+        <v>86.67992047713717</v>
       </c>
       <c r="D24">
-        <v>501</v>
+        <v>465</v>
       </c>
       <c r="E24">
-        <v>502</v>
+        <v>473</v>
       </c>
       <c r="F24">
-        <v>1343.38</v>
+        <v>304.45</v>
       </c>
       <c r="G24">
-        <v>1.234907178396219</v>
+        <v>0.5436284006470684</v>
       </c>
       <c r="H24">
-        <v>1.509028861881832</v>
+        <v>1.439691958590364</v>
       </c>
       <c r="I24">
-        <v>3.86</v>
+        <v>1.3</v>
       </c>
       <c r="J24">
-        <v>0.7100980204410158</v>
+        <v>-0.7894317745235507</v>
       </c>
       <c r="K24">
-        <v>4.22</v>
+        <v>1.79</v>
       </c>
       <c r="L24">
-        <v>1.083024474432137</v>
+        <v>-0.1359136421544107</v>
       </c>
       <c r="M24">
-        <v>1330.330004882813</v>
+        <v>300.197998046875</v>
       </c>
       <c r="N24">
-        <v>1297.799505615234</v>
+        <v>292.7754989624024</v>
       </c>
       <c r="O24">
-        <v>1310.078598632813</v>
+        <v>281.4825994873047</v>
       </c>
       <c r="P24" t="b">
         <v>1</v>
       </c>
       <c r="Q24">
-        <v>1168.966400756836</v>
+        <v>244.2887502288818</v>
       </c>
       <c r="R24">
         <v>1.03</v>
       </c>
       <c r="S24">
-        <v>0.99</v>
+        <v>1.04</v>
       </c>
       <c r="U24">
         <v>0</v>
       </c>
       <c r="V24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W24" t="b">
         <v>1</v>
@@ -3665,58 +3674,808 @@
         <v>0</v>
       </c>
       <c r="Y24">
-        <v>562.04</v>
+        <v>155.96</v>
       </c>
       <c r="Z24">
-        <v>1769.14</v>
+        <v>306.34</v>
       </c>
       <c r="AA24">
-        <v>30.88</v>
+        <v>18.44</v>
       </c>
       <c r="AB24">
-        <v>7.6</v>
+        <v>18.45</v>
       </c>
       <c r="AC24">
-        <v>12.1</v>
+        <v>13.48</v>
       </c>
       <c r="AD24">
-        <v>4.8</v>
+        <v>46.25</v>
       </c>
       <c r="AE24">
-        <v>41.7</v>
+        <v>29.49</v>
       </c>
       <c r="AF24">
-        <v>-7.01</v>
+        <v>-56.51</v>
       </c>
       <c r="AG24">
-        <v>0.4</v>
+        <v>101.69</v>
       </c>
       <c r="AH24">
-        <v>0.95</v>
+        <v>-11.61</v>
       </c>
       <c r="AI24" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="AJ24" t="s">
+        <v>87</v>
+      </c>
+      <c r="AK24" t="s">
+        <v>111</v>
+      </c>
+      <c r="AL24" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM24">
+        <v>11.6</v>
+      </c>
+      <c r="AN24">
+        <v>13.02</v>
+      </c>
+      <c r="AO24">
+        <v>12.24</v>
+      </c>
+      <c r="AP24">
+        <v>30.27511746339932</v>
+      </c>
+    </row>
+    <row r="25" spans="1:42">
+      <c r="A25" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25">
+        <v>95.02982107355865</v>
+      </c>
+      <c r="C25">
+        <v>80.51689860834989</v>
+      </c>
+      <c r="D25">
+        <v>442</v>
+      </c>
+      <c r="E25">
+        <v>476</v>
+      </c>
+      <c r="F25">
+        <v>321</v>
+      </c>
+      <c r="G25">
+        <v>0.4739237080370798</v>
+      </c>
+      <c r="H25">
+        <v>1.045573857030769</v>
+      </c>
+      <c r="I25">
+        <v>1.86</v>
+      </c>
+      <c r="J25">
+        <v>0.02871576971783195</v>
+      </c>
+      <c r="K25">
+        <v>1.44</v>
+      </c>
+      <c r="L25">
+        <v>-0.6545314872172948</v>
+      </c>
+      <c r="M25">
+        <v>308.0159973144531</v>
+      </c>
+      <c r="N25">
+        <v>300.9290008544922</v>
+      </c>
+      <c r="O25">
+        <v>294.9806005859375</v>
+      </c>
+      <c r="P25" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q25">
+        <v>271.0831507110595</v>
+      </c>
+      <c r="R25">
+        <v>1.02</v>
+      </c>
+      <c r="S25">
+        <v>1.02</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25" t="b">
+        <v>0</v>
+      </c>
+      <c r="W25" t="b">
+        <v>1</v>
+      </c>
+      <c r="X25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>184.81</v>
+      </c>
+      <c r="Z25">
+        <v>334</v>
+      </c>
+      <c r="AA25">
+        <v>18.58</v>
+      </c>
+      <c r="AB25">
+        <v>6.18</v>
+      </c>
+      <c r="AC25">
+        <v>15.14</v>
+      </c>
+      <c r="AD25">
+        <v>33.42</v>
+      </c>
+      <c r="AE25">
+        <v>20.58</v>
+      </c>
+      <c r="AF25">
+        <v>-11.93</v>
+      </c>
+      <c r="AG25">
+        <v>0.71</v>
+      </c>
+      <c r="AH25">
+        <v>15.04</v>
+      </c>
+      <c r="AI25" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ25" t="s">
         <v>90</v>
       </c>
-      <c r="AK24" t="s">
-        <v>107</v>
-      </c>
-      <c r="AL24" t="s">
-        <v>108</v>
-      </c>
-      <c r="AM24">
-        <v>19.75</v>
-      </c>
-      <c r="AN24">
-        <v>73.12</v>
-      </c>
-      <c r="AO24">
-        <v>270.23</v>
-      </c>
-      <c r="AP24">
-        <v>8.16652691362302</v>
+      <c r="AK25" t="s">
+        <v>104</v>
+      </c>
+      <c r="AL25" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM25">
+        <v>11.34</v>
+      </c>
+      <c r="AN25">
+        <v>15.4</v>
+      </c>
+      <c r="AO25">
+        <v>35.8</v>
+      </c>
+      <c r="AP25">
+        <v>28.94494376205292</v>
+      </c>
+    </row>
+    <row r="26" spans="1:42">
+      <c r="A26" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26">
+        <v>91.65009940357854</v>
+      </c>
+      <c r="C26">
+        <v>82.50497017892644</v>
+      </c>
+      <c r="D26">
+        <v>364</v>
+      </c>
+      <c r="E26">
+        <v>395</v>
+      </c>
+      <c r="F26">
+        <v>393.62</v>
+      </c>
+      <c r="G26">
+        <v>0.3446290566811357</v>
+      </c>
+      <c r="H26">
+        <v>1.284044555200062</v>
+      </c>
+      <c r="I26">
+        <v>1.64</v>
+      </c>
+      <c r="J26">
+        <v>-0.2926993369484258</v>
+      </c>
+      <c r="K26">
+        <v>1.47</v>
+      </c>
+      <c r="L26">
+        <v>-0.6100785290690475</v>
+      </c>
+      <c r="M26">
+        <v>403.4039978027344</v>
+      </c>
+      <c r="N26">
+        <v>397.201496887207</v>
+      </c>
+      <c r="O26">
+        <v>374.897998046875</v>
+      </c>
+      <c r="P26" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q26">
+        <v>321.2079998779297</v>
+      </c>
+      <c r="R26">
+        <v>1.02</v>
+      </c>
+      <c r="S26">
+        <v>1.06</v>
+      </c>
+      <c r="U26">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="V26" t="b">
+        <v>0</v>
+      </c>
+      <c r="W26" t="b">
+        <v>0</v>
+      </c>
+      <c r="X26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>227.08</v>
+      </c>
+      <c r="Z26">
+        <v>424.94</v>
+      </c>
+      <c r="AA26">
+        <v>58.65</v>
+      </c>
+      <c r="AB26">
+        <v>17.22</v>
+      </c>
+      <c r="AC26">
+        <v>17.32</v>
+      </c>
+      <c r="AD26">
+        <v>20.92</v>
+      </c>
+      <c r="AE26">
+        <v>13.47</v>
+      </c>
+      <c r="AF26" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG26" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH26" t="s">
+        <v>72</v>
+      </c>
+      <c r="AI26" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ26" t="s">
+        <v>91</v>
+      </c>
+      <c r="AK26" t="s">
+        <v>112</v>
+      </c>
+      <c r="AL26" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM26">
+        <v>6.44</v>
+      </c>
+      <c r="AN26">
+        <v>10.16</v>
+      </c>
+      <c r="AO26">
+        <v>57.76</v>
+      </c>
+      <c r="AP26">
+        <v>28.49057060172095</v>
+      </c>
+    </row>
+    <row r="27" spans="1:42">
+      <c r="A27" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27">
+        <v>91.45129224652088</v>
+      </c>
+      <c r="C27">
+        <v>35.98409542743538</v>
+      </c>
+      <c r="D27">
+        <v>330</v>
+      </c>
+      <c r="E27">
+        <v>291</v>
+      </c>
+      <c r="F27">
+        <v>287.1</v>
+      </c>
+      <c r="G27">
+        <v>0.4372830534728996</v>
+      </c>
+      <c r="H27">
+        <v>-0.03631978127241955</v>
+      </c>
+      <c r="I27">
+        <v>1.06</v>
+      </c>
+      <c r="J27">
+        <v>-1.140066436341286</v>
+      </c>
+      <c r="K27">
+        <v>1.24</v>
+      </c>
+      <c r="L27">
+        <v>-0.9508845415389426</v>
+      </c>
+      <c r="M27">
+        <v>279.6960021972656</v>
+      </c>
+      <c r="N27">
+        <v>276.9550018310547</v>
+      </c>
+      <c r="O27">
+        <v>276.5810009765625</v>
+      </c>
+      <c r="P27" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q27">
+        <v>253.9902502441406</v>
+      </c>
+      <c r="R27">
+        <v>1.01</v>
+      </c>
+      <c r="S27">
+        <v>1</v>
+      </c>
+      <c r="U27">
+        <v>2.222222222222222</v>
+      </c>
+      <c r="V27" t="b">
+        <v>1</v>
+      </c>
+      <c r="W27" t="b">
+        <v>1</v>
+      </c>
+      <c r="X27" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y27">
+        <v>194.04</v>
+      </c>
+      <c r="Z27">
+        <v>290.79</v>
+      </c>
+      <c r="AA27">
+        <v>103.47</v>
+      </c>
+      <c r="AB27">
+        <v>10.36</v>
+      </c>
+      <c r="AC27">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="AD27">
+        <v>15.91</v>
+      </c>
+      <c r="AE27">
+        <v>13.62</v>
+      </c>
+      <c r="AF27" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG27" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH27" t="s">
+        <v>72</v>
+      </c>
+      <c r="AI27" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ27" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK27" t="s">
+        <v>113</v>
+      </c>
+      <c r="AL27" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM27">
+        <v>10.33</v>
+      </c>
+      <c r="AN27">
+        <v>10.37</v>
+      </c>
+      <c r="AO27">
+        <v>0.39</v>
+      </c>
+      <c r="AP27">
+        <v>19.46044893876378</v>
+      </c>
+    </row>
+    <row r="28" spans="1:42">
+      <c r="A28" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28">
+        <v>92.6441351888668</v>
+      </c>
+      <c r="C28">
+        <v>72.56461232604374</v>
+      </c>
+      <c r="D28">
+        <v>446</v>
+      </c>
+      <c r="E28">
+        <v>447</v>
+      </c>
+      <c r="F28">
+        <v>139.34</v>
+      </c>
+      <c r="G28">
+        <v>0.3608213247450959</v>
+      </c>
+      <c r="H28">
+        <v>0.8191607773413427</v>
+      </c>
+      <c r="I28">
+        <v>2.5</v>
+      </c>
+      <c r="J28">
+        <v>0.9637415345651261</v>
+      </c>
+      <c r="K28">
+        <v>1.73</v>
+      </c>
+      <c r="L28">
+        <v>-0.2248195584509051</v>
+      </c>
+      <c r="M28">
+        <v>140.2740020751953</v>
+      </c>
+      <c r="N28">
+        <v>127.4040004730225</v>
+      </c>
+      <c r="O28">
+        <v>123.713800201416</v>
+      </c>
+      <c r="P28" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q28">
+        <v>118.7573499679565</v>
+      </c>
+      <c r="R28">
+        <v>1.1</v>
+      </c>
+      <c r="S28">
+        <v>1.03</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28" t="b">
+        <v>0</v>
+      </c>
+      <c r="W28" t="b">
+        <v>1</v>
+      </c>
+      <c r="X28" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y28">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="Z28">
+        <v>144</v>
+      </c>
+      <c r="AA28">
+        <v>11.5</v>
+      </c>
+      <c r="AB28">
+        <v>11.82</v>
+      </c>
+      <c r="AC28">
+        <v>15.63</v>
+      </c>
+      <c r="AD28">
+        <v>7.95</v>
+      </c>
+      <c r="AE28">
+        <v>20.47</v>
+      </c>
+      <c r="AF28">
+        <v>1.67</v>
+      </c>
+      <c r="AG28">
+        <v>-13.04</v>
+      </c>
+      <c r="AH28">
+        <v>21.91</v>
+      </c>
+      <c r="AI28" t="s">
+        <v>85</v>
+      </c>
+      <c r="AJ28" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK28" t="s">
+        <v>114</v>
+      </c>
+      <c r="AL28" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM28">
+        <v>12.5</v>
+      </c>
+      <c r="AN28">
+        <v>13.55</v>
+      </c>
+      <c r="AO28">
+        <v>8.4</v>
+      </c>
+      <c r="AP28">
+        <v>19.04841923368722</v>
+      </c>
+    </row>
+    <row r="29" spans="1:42">
+      <c r="A29" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29">
+        <v>97.01789264413519</v>
+      </c>
+      <c r="C29">
+        <v>99.20477137176938</v>
+      </c>
+      <c r="D29">
+        <v>74</v>
+      </c>
+      <c r="E29">
+        <v>67</v>
+      </c>
+      <c r="F29">
+        <v>252.53</v>
+      </c>
+      <c r="G29">
+        <v>0.6119317841040106</v>
+      </c>
+      <c r="H29">
+        <v>1.47177272879975</v>
+      </c>
+      <c r="I29">
+        <v>1.83</v>
+      </c>
+      <c r="J29">
+        <v>-0.01511356300938501</v>
+      </c>
+      <c r="K29">
+        <v>2.67</v>
+      </c>
+      <c r="L29">
+        <v>1.16803979686084</v>
+      </c>
+      <c r="M29">
+        <v>250.2600006103516</v>
+      </c>
+      <c r="N29">
+        <v>242.3059997558594</v>
+      </c>
+      <c r="O29">
+        <v>212.7442004394531</v>
+      </c>
+      <c r="P29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q29">
+        <v>175.955950088501</v>
+      </c>
+      <c r="R29">
+        <v>1.03</v>
+      </c>
+      <c r="S29">
+        <v>1.14</v>
+      </c>
+      <c r="U29">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="V29" t="b">
+        <v>0</v>
+      </c>
+      <c r="W29" t="b">
+        <v>1</v>
+      </c>
+      <c r="X29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>118.86</v>
+      </c>
+      <c r="Z29">
+        <v>260.87</v>
+      </c>
+      <c r="AA29">
+        <v>709.3099999999999</v>
+      </c>
+      <c r="AB29">
+        <v>7.13</v>
+      </c>
+      <c r="AC29">
+        <v>12.52</v>
+      </c>
+      <c r="AD29">
+        <v>7.64</v>
+      </c>
+      <c r="AE29">
+        <v>85.36</v>
+      </c>
+      <c r="AF29" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG29" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH29" t="s">
+        <v>72</v>
+      </c>
+      <c r="AI29" t="s">
+        <v>86</v>
+      </c>
+      <c r="AJ29" t="s">
+        <v>90</v>
+      </c>
+      <c r="AK29" t="s">
+        <v>104</v>
+      </c>
+      <c r="AL29" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM29">
+        <v>4.35</v>
+      </c>
+      <c r="AN29">
+        <v>7.16</v>
+      </c>
+      <c r="AO29">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="AP29">
+        <v>18.46125027635196</v>
+      </c>
+    </row>
+    <row r="30" spans="1:42">
+      <c r="A30" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30">
+        <v>94.23459244532803</v>
+      </c>
+      <c r="C30">
+        <v>86.87872763419483</v>
+      </c>
+      <c r="D30">
+        <v>328</v>
+      </c>
+      <c r="E30">
+        <v>332</v>
+      </c>
+      <c r="F30">
+        <v>84.25</v>
+      </c>
+      <c r="G30">
+        <v>0.393256967104373</v>
+      </c>
+      <c r="H30">
+        <v>1.371010944050678</v>
+      </c>
+      <c r="I30">
+        <v>1.1</v>
+      </c>
+      <c r="J30">
+        <v>-1.08162732603833</v>
+      </c>
+      <c r="K30">
+        <v>1.11</v>
+      </c>
+      <c r="L30">
+        <v>-1.143514026848014</v>
+      </c>
+      <c r="M30">
+        <v>84.13200073242187</v>
+      </c>
+      <c r="N30">
+        <v>82.34449996948243</v>
+      </c>
+      <c r="O30">
+        <v>76.81040008544922</v>
+      </c>
+      <c r="P30" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q30">
+        <v>70.84215000152588</v>
+      </c>
+      <c r="R30">
+        <v>1.02</v>
+      </c>
+      <c r="S30">
+        <v>1.07</v>
+      </c>
+      <c r="U30">
+        <v>11.66666666666667</v>
+      </c>
+      <c r="V30" t="b">
+        <v>1</v>
+      </c>
+      <c r="W30" t="b">
+        <v>1</v>
+      </c>
+      <c r="X30" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y30">
+        <v>48.65</v>
+      </c>
+      <c r="Z30">
+        <v>86.42</v>
+      </c>
+      <c r="AA30">
+        <v>20.1</v>
+      </c>
+      <c r="AB30">
+        <v>24.51</v>
+      </c>
+      <c r="AC30">
+        <v>1.46</v>
+      </c>
+      <c r="AD30">
+        <v>17.17</v>
+      </c>
+      <c r="AE30">
+        <v>31</v>
+      </c>
+      <c r="AF30" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG30" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH30" t="s">
+        <v>72</v>
+      </c>
+      <c r="AI30" t="s">
+        <v>83</v>
+      </c>
+      <c r="AJ30" t="s">
+        <v>90</v>
+      </c>
+      <c r="AK30" t="s">
+        <v>115</v>
+      </c>
+      <c r="AL30" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM30">
+        <v>6.13</v>
+      </c>
+      <c r="AN30">
+        <v>2.98</v>
+      </c>
+      <c r="AO30">
+        <v>-51.39</v>
+      </c>
+      <c r="AP30">
+        <v>11.6238758500156</v>
       </c>
     </row>
   </sheetData>
